--- a/config/sprints.xlsx
+++ b/config/sprints.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optional. Placeholders: {team}, {project}, {number}. Default: {team} Sprint {number}</t>
+          <t>Optional. Placeholders: {team}, {project}, {number}. Default: {team} Sprint {number}. {number} is written with at least 2 digits: 01, 02 ... 10.</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>That sprint's start date. Later sprints follow on back to back, one sprint length apart.</t>
+          <t>That sprint's start date, as an Excel date or text like 2026-01-05. Later sprints follow on back to back, one sprint length apart.</t>
         </is>
       </c>
     </row>
